--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V87"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6523,6 +6523,76 @@
         <v>-0.01</v>
       </c>
       <c r="V87" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-09-06 13:29:43</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D88" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G88" t="n">
+        <v>99.155</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I88" t="n">
+        <v>66.96327640924891</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.481649295151471</v>
+      </c>
+      <c r="K88" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="L88" t="n">
+        <v>50</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N88" t="n">
+        <v>50</v>
+      </c>
+      <c r="O88" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R88" t="n">
+        <v>95.929</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T88" t="n">
+        <v>4430.96</v>
+      </c>
+      <c r="U88" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V88" t="n">
         <v>0.16</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6594,6 +6594,76 @@
       </c>
       <c r="V88" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:41:13</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D89" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G89" t="n">
+        <v>99.1627</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I89" t="n">
+        <v>66.88785898799574</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.465368050227108</v>
+      </c>
+      <c r="K89" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="L89" t="n">
+        <v>50</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O89" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R89" t="n">
+        <v>97.53</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T89" t="n">
+        <v>4401.89</v>
+      </c>
+      <c r="U89" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6664,6 +6664,76 @@
       </c>
       <c r="V89" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-08 13:35:49</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D90" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G90" t="n">
+        <v>98.8267</v>
+      </c>
+      <c r="H90" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="I90" t="n">
+        <v>66.43442992338892</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.476933502847958</v>
+      </c>
+      <c r="K90" t="n">
+        <v>62.26</v>
+      </c>
+      <c r="L90" t="n">
+        <v>50</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N90" t="n">
+        <v>50</v>
+      </c>
+      <c r="O90" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="P90" t="n">
+        <v/>
+      </c>
+      <c r="Q90" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R90" t="n">
+        <v>98.131</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T90" t="n">
+        <v>4422.54</v>
+      </c>
+      <c r="U90" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V90" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6714,9 +6714,6 @@
       <c r="O90" t="n">
         <v>17.72</v>
       </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="n">
         <v>117.92</v>
       </c>
@@ -6734,6 +6731,76 @@
       </c>
       <c r="V90" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-09 13:42:55</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D91" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G91" t="n">
+        <v>98.72750000000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="I91" t="n">
+        <v>66.10430463576159</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.459812152406343</v>
+      </c>
+      <c r="K91" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="L91" t="n">
+        <v>50</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="N91" t="n">
+        <v>50</v>
+      </c>
+      <c r="O91" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R91" t="n">
+        <v>98.934</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T91" t="n">
+        <v>4391.97</v>
+      </c>
+      <c r="U91" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V91" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6801,6 +6801,76 @@
       </c>
       <c r="V91" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:35:57</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D92" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="G92" t="n">
+        <v>98.7287</v>
+      </c>
+      <c r="H92" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="I92" t="n">
+        <v>65.29418707583358</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2.478669720916947</v>
+      </c>
+      <c r="K92" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="L92" t="n">
+        <v>50</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>50</v>
+      </c>
+      <c r="O92" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R92" t="n">
+        <v>100.421</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T92" t="n">
+        <v>4425.64</v>
+      </c>
+      <c r="U92" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V92" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V92"/>
+  <dimension ref="A1:V93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6871,6 +6871,76 @@
       </c>
       <c r="V92" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-11 13:37:15</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D93" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G93" t="n">
+        <v>99.03189999999999</v>
+      </c>
+      <c r="H93" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I93" t="n">
+        <v>67.95865956780457</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2.430615685330078</v>
+      </c>
+      <c r="K93" t="n">
+        <v>55.57</v>
+      </c>
+      <c r="L93" t="n">
+        <v>50</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="N93" t="n">
+        <v>50</v>
+      </c>
+      <c r="O93" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="P93" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R93" t="n">
+        <v>105.944</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T93" t="n">
+        <v>4339.84</v>
+      </c>
+      <c r="U93" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V93" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V93"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6941,6 +6941,76 @@
       </c>
       <c r="V93" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-12 13:24:21</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D94" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G94" t="n">
+        <v>99.09010000000001</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I94" t="n">
+        <v>67.46858029480218</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.435381883964626</v>
+      </c>
+      <c r="K94" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="L94" t="n">
+        <v>50</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="N94" t="n">
+        <v>50</v>
+      </c>
+      <c r="O94" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R94" t="n">
+        <v>104.246</v>
+      </c>
+      <c r="S94" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T94" t="n">
+        <v>4348.35</v>
+      </c>
+      <c r="U94" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V94" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7010,6 +7010,76 @@
         <v>-0.01</v>
       </c>
       <c r="V94" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-13 13:39:43</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D95" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G95" t="n">
+        <v>99.09010000000001</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I95" t="n">
+        <v>67.46858029480218</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2.435381883964626</v>
+      </c>
+      <c r="K95" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="L95" t="n">
+        <v>50</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="N95" t="n">
+        <v>50</v>
+      </c>
+      <c r="O95" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R95" t="n">
+        <v>104.246</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T95" t="n">
+        <v>4348.35</v>
+      </c>
+      <c r="U95" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V95" t="n">
         <v>0.01</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V95"/>
+  <dimension ref="A1:V96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7081,6 +7081,76 @@
       </c>
       <c r="V95" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-14 13:47:36</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D96" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G96" t="n">
+        <v>99.315</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I96" t="n">
+        <v>67.8730407523511</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2.425272614240348</v>
+      </c>
+      <c r="K96" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="L96" t="n">
+        <v>50</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="N96" t="n">
+        <v>50</v>
+      </c>
+      <c r="O96" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R96" t="n">
+        <v>106.614</v>
+      </c>
+      <c r="S96" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T96" t="n">
+        <v>4330.3</v>
+      </c>
+      <c r="U96" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V96" t="n">
+        <v>0.23</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V96"/>
+  <dimension ref="A1:V97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7151,6 +7151,76 @@
       </c>
       <c r="V96" t="n">
         <v>0.23</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-15 13:48:54</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D97" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>99.6036</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="I97" t="n">
+        <v>67.98845119443126</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2.406930310446992</v>
+      </c>
+      <c r="K97" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="L97" t="n">
+        <v>50</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="N97" t="n">
+        <v>50</v>
+      </c>
+      <c r="O97" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R97" t="n">
+        <v>107.234</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T97" t="n">
+        <v>4297.55</v>
+      </c>
+      <c r="U97" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V97" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V97"/>
+  <dimension ref="A1:V98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7221,6 +7221,76 @@
       </c>
       <c r="V97" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-16 13:38:11</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D98" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G98" t="n">
+        <v>99.6087</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I98" t="n">
+        <v>66.94401484689143</v>
+      </c>
+      <c r="J98" t="n">
+        <v>2.424320494654129</v>
+      </c>
+      <c r="K98" t="n">
+        <v>43.16</v>
+      </c>
+      <c r="L98" t="n">
+        <v>50</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="N98" t="n">
+        <v>50</v>
+      </c>
+      <c r="O98" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R98" t="n">
+        <v>107.972</v>
+      </c>
+      <c r="S98" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T98" t="n">
+        <v>4328.6</v>
+      </c>
+      <c r="U98" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V98" t="n">
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V98"/>
+  <dimension ref="A1:V99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7291,6 +7291,76 @@
       </c>
       <c r="V98" t="n">
         <v>-0.02</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-17 13:44:11</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D99" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G99" t="n">
+        <v>100.2658</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I99" t="n">
+        <v>67.48044604994502</v>
+      </c>
+      <c r="J99" t="n">
+        <v>2.406331035178018</v>
+      </c>
+      <c r="K99" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="L99" t="n">
+        <v>50</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="N99" t="n">
+        <v>50</v>
+      </c>
+      <c r="O99" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R99" t="n">
+        <v>105.422</v>
+      </c>
+      <c r="S99" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T99" t="n">
+        <v>4296.48</v>
+      </c>
+      <c r="U99" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V99" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V99"/>
+  <dimension ref="A1:V100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7361,6 +7361,76 @@
       </c>
       <c r="V99" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-18 13:32:54</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C100" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D100" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F100" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G100" t="n">
+        <v>100.3127</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I100" t="n">
+        <v>65.88009664753851</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2.443351684971633</v>
+      </c>
+      <c r="K100" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="N100" t="n">
+        <v>50</v>
+      </c>
+      <c r="O100" t="n">
+        <v>17.73</v>
+      </c>
+      <c r="P100" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R100" t="n">
+        <v>98.886</v>
+      </c>
+      <c r="S100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T100" t="n">
+        <v>4362.58</v>
+      </c>
+      <c r="U100" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V100" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V100"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7431,6 +7431,76 @@
       </c>
       <c r="V100" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-19 13:29:33</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D101" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G101" t="n">
+        <v>100.2167</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I101" t="n">
+        <v>66.08739622641509</v>
+      </c>
+      <c r="J101" t="n">
+        <v>2.452150390088995</v>
+      </c>
+      <c r="K101" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N101" t="n">
+        <v>50</v>
+      </c>
+      <c r="O101" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R101" t="n">
+        <v>98.73399999999999</v>
+      </c>
+      <c r="S101" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T101" t="n">
+        <v>4378.29</v>
+      </c>
+      <c r="U101" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V101" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V101"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7500,6 +7500,76 @@
         <v>-0.01</v>
       </c>
       <c r="V101" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:42:54</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D102" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G102" t="n">
+        <v>100.2167</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I102" t="n">
+        <v>66.08739622641509</v>
+      </c>
+      <c r="J102" t="n">
+        <v>2.452150390088995</v>
+      </c>
+      <c r="K102" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N102" t="n">
+        <v>50</v>
+      </c>
+      <c r="O102" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R102" t="n">
+        <v>98.73399999999999</v>
+      </c>
+      <c r="S102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T102" t="n">
+        <v>4378.29</v>
+      </c>
+      <c r="U102" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V102" t="n">
         <v>-0.01</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V102"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7571,6 +7571,76 @@
       </c>
       <c r="V102" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-21 13:54:15</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C103" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D103" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G103" t="n">
+        <v>100.3296</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="I103" t="n">
+        <v>65.95350598212933</v>
+      </c>
+      <c r="J103" t="n">
+        <v>2.439055945426746</v>
+      </c>
+      <c r="K103" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N103" t="n">
+        <v>50</v>
+      </c>
+      <c r="O103" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="P103" t="n">
+        <v/>
+      </c>
+      <c r="Q103" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R103" t="n">
+        <v>98.056</v>
+      </c>
+      <c r="S103" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T103" t="n">
+        <v>4354.91</v>
+      </c>
+      <c r="U103" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V103" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V103"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7621,9 +7621,6 @@
       <c r="O103" t="n">
         <v>17.76</v>
       </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="n">
         <v>117.92</v>
       </c>
@@ -7641,6 +7638,76 @@
       </c>
       <c r="V103" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-22 13:51:29</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D104" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G104" t="n">
+        <v>100.3684</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I104" t="n">
+        <v>65.99177080158488</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.425317419867935</v>
+      </c>
+      <c r="K104" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N104" t="n">
+        <v>50</v>
+      </c>
+      <c r="O104" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R104" t="n">
+        <v>97.628</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T104" t="n">
+        <v>4330.38</v>
+      </c>
+      <c r="U104" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V104" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V104"/>
+  <dimension ref="A1:V105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7708,6 +7708,76 @@
       </c>
       <c r="V104" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-09-23 13:29:14</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D105" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G105" t="n">
+        <v>100.7105</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I105" t="n">
+        <v>65.29632972322501</v>
+      </c>
+      <c r="J105" t="n">
+        <v>2.431209359895603</v>
+      </c>
+      <c r="K105" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>-0.198</v>
+      </c>
+      <c r="N105" t="n">
+        <v>100</v>
+      </c>
+      <c r="O105" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R105" t="n">
+        <v>94.63800000000001</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T105" t="n">
+        <v>4340.9</v>
+      </c>
+      <c r="U105" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V105" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V105"/>
+  <dimension ref="A1:V106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7778,6 +7778,76 @@
       </c>
       <c r="V105" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-09-24 13:51:26</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C106" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D106" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G106" t="n">
+        <v>101.1359</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I106" t="n">
+        <v>66.82368544234669</v>
+      </c>
+      <c r="J106" t="n">
+        <v>2.398630067936533</v>
+      </c>
+      <c r="K106" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N106" t="n">
+        <v>50</v>
+      </c>
+      <c r="O106" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R106" t="n">
+        <v>98.13200000000001</v>
+      </c>
+      <c r="S106" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T106" t="n">
+        <v>4282.73</v>
+      </c>
+      <c r="U106" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V106"/>
+  <dimension ref="A1:V107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7848,6 +7848,76 @@
       </c>
       <c r="V106" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:48:55</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C107" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D107" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G107" t="n">
+        <v>101.2297</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I107" t="n">
+        <v>67.02729839974897</v>
+      </c>
+      <c r="J107" t="n">
+        <v>2.392799735646797</v>
+      </c>
+      <c r="K107" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N107" t="n">
+        <v>50</v>
+      </c>
+      <c r="O107" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R107" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="S107" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T107" t="n">
+        <v>4272.32</v>
+      </c>
+      <c r="U107" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V107" t="n">
+        <v>-0.01</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V107"/>
+  <dimension ref="A1:V108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7918,6 +7918,76 @@
       </c>
       <c r="V107" t="n">
         <v>-0.01</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-09-26 13:50:52</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D108" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F108" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G108" t="n">
+        <v>101.0343</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I108" t="n">
+        <v>66.64261275272162</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2.399968636060689</v>
+      </c>
+      <c r="K108" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N108" t="n">
+        <v>50</v>
+      </c>
+      <c r="O108" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P108" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R108" t="n">
+        <v>97.48399999999999</v>
+      </c>
+      <c r="S108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T108" t="n">
+        <v>4285.12</v>
+      </c>
+      <c r="U108" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V108" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V108"/>
+  <dimension ref="A1:V109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7987,6 +7987,76 @@
         <v>-0.01</v>
       </c>
       <c r="V108" t="n">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-09-27 14:13:31</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D109" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G109" t="n">
+        <v>101.0343</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I109" t="n">
+        <v>66.64261275272162</v>
+      </c>
+      <c r="J109" t="n">
+        <v>2.399968636060689</v>
+      </c>
+      <c r="K109" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N109" t="n">
+        <v>50</v>
+      </c>
+      <c r="O109" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R109" t="n">
+        <v>97.48399999999999</v>
+      </c>
+      <c r="S109" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T109" t="n">
+        <v>4285.12</v>
+      </c>
+      <c r="U109" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V109" t="n">
         <v>-0.21</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V109"/>
+  <dimension ref="A1:V110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8058,6 +8058,76 @@
       </c>
       <c r="V109" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-09-28 14:19:10</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D110" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="G110" t="n">
+        <v>101.1739</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="I110" t="n">
+        <v>67.75965595585849</v>
+      </c>
+      <c r="J110" t="n">
+        <v>2.338489714308117</v>
+      </c>
+      <c r="K110" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N110" t="n">
+        <v>50</v>
+      </c>
+      <c r="O110" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R110" t="n">
+        <v>98.863</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T110" t="n">
+        <v>4175.35</v>
+      </c>
+      <c r="U110" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V110"/>
+  <dimension ref="A1:V111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8128,6 +8128,76 @@
       </c>
       <c r="V110" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:34:44</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D111" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G111" t="n">
+        <v>101.2567</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" t="n">
+        <v>68.02166776099803</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2.32086430055615</v>
+      </c>
+      <c r="K111" t="n">
+        <v>42.36</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="N111" t="n">
+        <v>50</v>
+      </c>
+      <c r="O111" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="P111" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R111" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="S111" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T111" t="n">
+        <v>4143.88</v>
+      </c>
+      <c r="U111" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V111"/>
+  <dimension ref="A1:V112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8198,6 +8198,76 @@
       </c>
       <c r="V111" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-09-30 14:17:28</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D112" t="n">
+        <v>120.2528524075522</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G112" t="n">
+        <v>101.2547</v>
+      </c>
+      <c r="H112" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I112" t="n">
+        <v>68.40657184894556</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2.343575153039222</v>
+      </c>
+      <c r="K112" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>-0.712</v>
+      </c>
+      <c r="N112" t="n">
+        <v>50</v>
+      </c>
+      <c r="O112" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>117.92</v>
+      </c>
+      <c r="R112" t="n">
+        <v>95.727</v>
+      </c>
+      <c r="S112" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T112" t="n">
+        <v>4184.43</v>
+      </c>
+      <c r="U112" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V112" t="n">
+        <v>-0.13</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V112"/>
+  <dimension ref="A1:V113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8268,6 +8268,76 @@
       </c>
       <c r="V112" t="n">
         <v>-0.13</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-02 14:41:01</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D113" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F113" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="G113" t="n">
+        <v>101.8811</v>
+      </c>
+      <c r="H113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I113" t="n">
+        <v>68.44142670157069</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2.342852662294384</v>
+      </c>
+      <c r="K113" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="L113" t="n">
+        <v>50</v>
+      </c>
+      <c r="M113" t="n">
+        <v>-0.418</v>
+      </c>
+      <c r="N113" t="n">
+        <v>50</v>
+      </c>
+      <c r="O113" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R113" t="n">
+        <v>101.483</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T113" t="n">
+        <v>4183.14</v>
+      </c>
+      <c r="U113" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V113" t="n">
+        <v>-0.16</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V113"/>
+  <dimension ref="A1:V114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8338,6 +8338,76 @@
       </c>
       <c r="V113" t="n">
         <v>-0.16</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-03 14:02:14</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D114" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G114" t="n">
+        <v>101.9303</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I114" t="n">
+        <v>68.59927079880676</v>
+      </c>
+      <c r="J114" t="n">
+        <v>2.318287976969907</v>
+      </c>
+      <c r="K114" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="L114" t="n">
+        <v>50</v>
+      </c>
+      <c r="M114" t="n">
+        <v>-0.362</v>
+      </c>
+      <c r="N114" t="n">
+        <v>50</v>
+      </c>
+      <c r="O114" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R114" t="n">
+        <v>102.653</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T114" t="n">
+        <v>4139.28</v>
+      </c>
+      <c r="U114" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V114" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V114"/>
+  <dimension ref="A1:V115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8407,6 +8407,76 @@
         <v>-0.01</v>
       </c>
       <c r="V114" t="n">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-04 14:37:12</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D115" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F115" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G115" t="n">
+        <v>101.9303</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I115" t="n">
+        <v>68.59927079880676</v>
+      </c>
+      <c r="J115" t="n">
+        <v>2.318287976969907</v>
+      </c>
+      <c r="K115" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="L115" t="n">
+        <v>50</v>
+      </c>
+      <c r="M115" t="n">
+        <v>-0.362</v>
+      </c>
+      <c r="N115" t="n">
+        <v>50</v>
+      </c>
+      <c r="O115" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R115" t="n">
+        <v>102.653</v>
+      </c>
+      <c r="S115" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T115" t="n">
+        <v>4139.28</v>
+      </c>
+      <c r="U115" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V115" t="n">
         <v>-0.11</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V115"/>
+  <dimension ref="A1:V116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8478,6 +8478,76 @@
       </c>
       <c r="V115" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-05 14:32:58</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D116" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G116" t="n">
+        <v>102.3538</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I116" t="n">
+        <v>67.65537459283388</v>
+      </c>
+      <c r="J116" t="n">
+        <v>2.326554615259677</v>
+      </c>
+      <c r="K116" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="L116" t="n">
+        <v>50</v>
+      </c>
+      <c r="M116" t="n">
+        <v>-0.362</v>
+      </c>
+      <c r="N116" t="n">
+        <v>50</v>
+      </c>
+      <c r="O116" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R116" t="n">
+        <v>101.479</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T116" t="n">
+        <v>4154.04</v>
+      </c>
+      <c r="U116" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V116"/>
+  <dimension ref="A1:V117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8548,6 +8548,76 @@
       </c>
       <c r="V116" t="n">
         <v>0.42</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-06 15:11:09</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D117" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G117" t="n">
+        <v>102.2757</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I117" t="n">
+        <v>68.11596832728472</v>
+      </c>
+      <c r="J117" t="n">
+        <v>2.312636867190519</v>
+      </c>
+      <c r="K117" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="L117" t="n">
+        <v>50</v>
+      </c>
+      <c r="M117" t="n">
+        <v>-0.348</v>
+      </c>
+      <c r="N117" t="n">
+        <v>50</v>
+      </c>
+      <c r="O117" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R117" t="n">
+        <v>99.54900000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T117" t="n">
+        <v>4129.19</v>
+      </c>
+      <c r="U117" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V117"/>
+  <dimension ref="A1:V118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8618,6 +8618,76 @@
       </c>
       <c r="V117" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:50:50</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D118" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F118" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G118" t="n">
+        <v>102.0832</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="I118" t="n">
+        <v>68.35968248718373</v>
+      </c>
+      <c r="J118" t="n">
+        <v>2.142329259823585</v>
+      </c>
+      <c r="K118" t="n">
+        <v>29.47</v>
+      </c>
+      <c r="L118" t="n">
+        <v>50</v>
+      </c>
+      <c r="M118" t="n">
+        <v>-0.472</v>
+      </c>
+      <c r="N118" t="n">
+        <v>50</v>
+      </c>
+      <c r="O118" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="P118" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R118" t="n">
+        <v>101.472</v>
+      </c>
+      <c r="S118" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T118" t="n">
+        <v>4133.71</v>
+      </c>
+      <c r="U118" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V118"/>
+  <dimension ref="A1:V119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8688,6 +8688,76 @@
       </c>
       <c r="V118" t="n">
         <v>0.24</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:59:33</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D119" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G119" t="n">
+        <v>102.3164</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I119" t="n">
+        <v>69.7026204564666</v>
+      </c>
+      <c r="J119" t="n">
+        <v>2.136732070856266</v>
+      </c>
+      <c r="K119" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="L119" t="n">
+        <v>50</v>
+      </c>
+      <c r="M119" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="N119" t="n">
+        <v>50</v>
+      </c>
+      <c r="O119" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R119" t="n">
+        <v>103.551</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T119" t="n">
+        <v>4122.91</v>
+      </c>
+      <c r="U119" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V119"/>
+  <dimension ref="A1:V120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8758,6 +8758,76 @@
       </c>
       <c r="V119" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:07:46</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D120" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G120" t="n">
+        <v>102.0656</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="I120" t="n">
+        <v>69.54476127320955</v>
+      </c>
+      <c r="J120" t="n">
+        <v>2.174062211718855</v>
+      </c>
+      <c r="K120" t="n">
+        <v>39.77</v>
+      </c>
+      <c r="L120" t="n">
+        <v>50</v>
+      </c>
+      <c r="M120" t="n">
+        <v>-0.748</v>
+      </c>
+      <c r="N120" t="n">
+        <v>50</v>
+      </c>
+      <c r="O120" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R120" t="n">
+        <v>103.526</v>
+      </c>
+      <c r="S120" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T120" t="n">
+        <v>4194.94</v>
+      </c>
+      <c r="U120" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V120" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V120"/>
+  <dimension ref="A1:V121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8828,6 +8828,76 @@
       </c>
       <c r="V120" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-10 14:41:11</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C121" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D121" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F121" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G121" t="n">
+        <v>102.2306</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I121" t="n">
+        <v>68.99802599111696</v>
+      </c>
+      <c r="J121" t="n">
+        <v>2.173777169688112</v>
+      </c>
+      <c r="K121" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="L121" t="n">
+        <v>50</v>
+      </c>
+      <c r="M121" t="n">
+        <v>-0.872</v>
+      </c>
+      <c r="N121" t="n">
+        <v>50</v>
+      </c>
+      <c r="O121" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R121" t="n">
+        <v>104.595</v>
+      </c>
+      <c r="S121" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T121" t="n">
+        <v>4194.39</v>
+      </c>
+      <c r="U121" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:V122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8897,6 +8897,76 @@
         <v>-0.01</v>
       </c>
       <c r="V121" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:48:09</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D122" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G122" t="n">
+        <v>102.2306</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I122" t="n">
+        <v>68.99802599111696</v>
+      </c>
+      <c r="J122" t="n">
+        <v>2.173777169688112</v>
+      </c>
+      <c r="K122" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="L122" t="n">
+        <v>50</v>
+      </c>
+      <c r="M122" t="n">
+        <v>-0.872</v>
+      </c>
+      <c r="N122" t="n">
+        <v>50</v>
+      </c>
+      <c r="O122" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="P122" t="n">
+        <v/>
+      </c>
+      <c r="Q122" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R122" t="n">
+        <v>104.595</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T122" t="n">
+        <v>4194.39</v>
+      </c>
+      <c r="U122" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V122" t="n">
         <v>0.1</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V122"/>
+  <dimension ref="A1:V123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8948,9 +8948,6 @@
       <c r="O122" t="n">
         <v>16.99</v>
       </c>
-      <c r="P122" t="n">
-        <v/>
-      </c>
       <c r="Q122" t="n">
         <v>146.21</v>
       </c>
@@ -8968,6 +8965,76 @@
       </c>
       <c r="V122" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:58:12</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D123" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G123" t="n">
+        <v>102.1867</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I123" t="n">
+        <v>68.83141447368421</v>
+      </c>
+      <c r="J123" t="n">
+        <v>2.168884811924086</v>
+      </c>
+      <c r="K123" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="L123" t="n">
+        <v>50</v>
+      </c>
+      <c r="M123" t="n">
+        <v>-0.872</v>
+      </c>
+      <c r="N123" t="n">
+        <v>50</v>
+      </c>
+      <c r="O123" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="P123" t="n">
+        <v/>
+      </c>
+      <c r="Q123" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R123" t="n">
+        <v>104.465</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T123" t="n">
+        <v>4184.95</v>
+      </c>
+      <c r="U123" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V123" t="n">
+        <v>-0.04</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V123"/>
+  <dimension ref="A1:V124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9015,9 +9015,6 @@
       <c r="O123" t="n">
         <v>16.99</v>
       </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="n">
         <v>146.21</v>
       </c>
@@ -9035,6 +9032,76 @@
       </c>
       <c r="V123" t="n">
         <v>-0.04</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:21:04</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D124" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="G124" t="n">
+        <v>102.3159</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I124" t="n">
+        <v>69.21409706173654</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2.173051608155312</v>
+      </c>
+      <c r="K124" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="L124" t="n">
+        <v>50</v>
+      </c>
+      <c r="M124" t="n">
+        <v>-0.836</v>
+      </c>
+      <c r="N124" t="n">
+        <v>50</v>
+      </c>
+      <c r="O124" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="P124" t="n">
+        <v/>
+      </c>
+      <c r="Q124" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R124" t="n">
+        <v>105.173</v>
+      </c>
+      <c r="S124" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>4192.99</v>
+      </c>
+      <c r="U124" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V124" t="n">
+        <v>-0.26</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V124"/>
+  <dimension ref="A1:V125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9082,9 +9082,6 @@
       <c r="O124" t="n">
         <v>16.69</v>
       </c>
-      <c r="P124" t="n">
-        <v/>
-      </c>
       <c r="Q124" t="n">
         <v>146.21</v>
       </c>
@@ -9102,6 +9099,76 @@
       </c>
       <c r="V124" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-14 13:48:30</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D125" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="G125" t="n">
+        <v>102.1161</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I125" t="n">
+        <v>70.43680108437817</v>
+      </c>
+      <c r="J125" t="n">
+        <v>2.154492780662749</v>
+      </c>
+      <c r="K125" t="n">
+        <v>42.01</v>
+      </c>
+      <c r="L125" t="n">
+        <v>50</v>
+      </c>
+      <c r="M125" t="n">
+        <v>-0.866</v>
+      </c>
+      <c r="N125" t="n">
+        <v>50</v>
+      </c>
+      <c r="O125" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="P125" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R125" t="n">
+        <v>106.172</v>
+      </c>
+      <c r="S125" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T125" t="n">
+        <v>4157.18</v>
+      </c>
+      <c r="U125" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V125" t="n">
+        <v>-0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V125"/>
+  <dimension ref="A1:V126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9169,6 +9169,76 @@
       </c>
       <c r="V125" t="n">
         <v>-0.08</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:33:42</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D126" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G126" t="n">
+        <v>102.1046</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I126" t="n">
+        <v>74.19903260480115</v>
+      </c>
+      <c r="J126" t="n">
+        <v>2.14651678638432</v>
+      </c>
+      <c r="K126" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="L126" t="n">
+        <v>50</v>
+      </c>
+      <c r="M126" t="n">
+        <v>-0.896</v>
+      </c>
+      <c r="N126" t="n">
+        <v>50</v>
+      </c>
+      <c r="O126" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R126" t="n">
+        <v>104.513</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T126" t="n">
+        <v>4141.79</v>
+      </c>
+      <c r="U126" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V126" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V126"/>
+  <dimension ref="A1:V127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9239,6 +9239,76 @@
       </c>
       <c r="V126" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-16 13:26:38</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D127" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G127" t="n">
+        <v>101.9215</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I127" t="n">
+        <v>72.31930006930008</v>
+      </c>
+      <c r="J127" t="n">
+        <v>2.163349813945293</v>
+      </c>
+      <c r="K127" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="L127" t="n">
+        <v>50</v>
+      </c>
+      <c r="M127" t="n">
+        <v>-0.878</v>
+      </c>
+      <c r="N127" t="n">
+        <v>50</v>
+      </c>
+      <c r="O127" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R127" t="n">
+        <v>105.431</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T127" t="n">
+        <v>4174.27</v>
+      </c>
+      <c r="U127" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V127" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V127"/>
+  <dimension ref="A1:V128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9309,6 +9309,76 @@
       </c>
       <c r="V127" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-17 13:19:11</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D128" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G128" t="n">
+        <v>101.7827</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I128" t="n">
+        <v>73.13048823322796</v>
+      </c>
+      <c r="J128" t="n">
+        <v>2.158053214755849</v>
+      </c>
+      <c r="K128" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="L128" t="n">
+        <v>50</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-0.756</v>
+      </c>
+      <c r="N128" t="n">
+        <v>50</v>
+      </c>
+      <c r="O128" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R128" t="n">
+        <v>109.928</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T128" t="n">
+        <v>4164.05</v>
+      </c>
+      <c r="U128" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V128" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V128"/>
+  <dimension ref="A1:V129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9378,6 +9378,76 @@
         <v>-0.01</v>
       </c>
       <c r="V128" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-18 13:25:54</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D129" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G129" t="n">
+        <v>101.7827</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I129" t="n">
+        <v>73.13048823322796</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2.158053214755849</v>
+      </c>
+      <c r="K129" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="L129" t="n">
+        <v>50</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-0.756</v>
+      </c>
+      <c r="N129" t="n">
+        <v>50</v>
+      </c>
+      <c r="O129" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R129" t="n">
+        <v>109.928</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T129" t="n">
+        <v>4164.05</v>
+      </c>
+      <c r="U129" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V129" t="n">
         <v>-0.19</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V129"/>
+  <dimension ref="A1:V130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9449,6 +9449,76 @@
       </c>
       <c r="V129" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-19 13:43:41</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C130" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D130" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G130" t="n">
+        <v>101.8203</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="I130" t="n">
+        <v>72.56503642039543</v>
+      </c>
+      <c r="J130" t="n">
+        <v>2.168444292422028</v>
+      </c>
+      <c r="K130" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="L130" t="n">
+        <v>50</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-0.756</v>
+      </c>
+      <c r="N130" t="n">
+        <v>50</v>
+      </c>
+      <c r="O130" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R130" t="n">
+        <v>107.82</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T130" t="n">
+        <v>4184.1</v>
+      </c>
+      <c r="U130" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V130"/>
+  <dimension ref="A1:V131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9519,6 +9519,76 @@
       </c>
       <c r="V130" t="n">
         <v>0.04</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-20 13:39:42</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C131" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D131" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G131" t="n">
+        <v>101.77</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I131" t="n">
+        <v>72.13986380303824</v>
+      </c>
+      <c r="J131" t="n">
+        <v>2.14115799620635</v>
+      </c>
+      <c r="K131" t="n">
+        <v>28.24</v>
+      </c>
+      <c r="L131" t="n">
+        <v>50</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-0.67</v>
+      </c>
+      <c r="N131" t="n">
+        <v>50</v>
+      </c>
+      <c r="O131" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="P131" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R131" t="n">
+        <v>110.041</v>
+      </c>
+      <c r="S131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T131" t="n">
+        <v>4131.45</v>
+      </c>
+      <c r="U131" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V131" t="n">
+        <v>-0.22</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V131"/>
+  <dimension ref="A1:V132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9589,6 +9589,76 @@
       </c>
       <c r="V131" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:43:05</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D132" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G132" t="n">
+        <v>101.7911</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I132" t="n">
+        <v>71.93937805730259</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2.134088953843921</v>
+      </c>
+      <c r="K132" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="L132" t="n">
+        <v>50</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-0.554</v>
+      </c>
+      <c r="N132" t="n">
+        <v>50</v>
+      </c>
+      <c r="O132" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R132" t="n">
+        <v>110.502</v>
+      </c>
+      <c r="S132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T132" t="n">
+        <v>4117.81</v>
+      </c>
+      <c r="U132" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V132"/>
+  <dimension ref="A1:V133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9659,6 +9659,76 @@
       </c>
       <c r="V132" t="n">
         <v>0.09</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-22 13:45:09</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C133" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D133" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G133" t="n">
+        <v>101.5592</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I133" t="n">
+        <v>72.84766672626498</v>
+      </c>
+      <c r="J133" t="n">
+        <v>2.111575815997595</v>
+      </c>
+      <c r="K133" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="L133" t="n">
+        <v>50</v>
+      </c>
+      <c r="M133" t="n">
+        <v>-0.428</v>
+      </c>
+      <c r="N133" t="n">
+        <v>50</v>
+      </c>
+      <c r="O133" t="n">
+        <v>17.39</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R133" t="n">
+        <v>111.169</v>
+      </c>
+      <c r="S133" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T133" t="n">
+        <v>4074.37</v>
+      </c>
+      <c r="U133" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V133" t="n">
+        <v>-0.14</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V133"/>
+  <dimension ref="A1:V134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9729,6 +9729,76 @@
       </c>
       <c r="V133" t="n">
         <v>-0.14</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-23 13:44:04</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D134" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="G134" t="n">
+        <v>101.684</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-1.06</v>
+      </c>
+      <c r="I134" t="n">
+        <v>73.94434239529758</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2.08626408366761</v>
+      </c>
+      <c r="K134" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="L134" t="n">
+        <v>50</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="N134" t="n">
+        <v>50</v>
+      </c>
+      <c r="O134" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R134" t="n">
+        <v>114.117</v>
+      </c>
+      <c r="S134" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T134" t="n">
+        <v>4025.53</v>
+      </c>
+      <c r="U134" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.06</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V134"/>
+  <dimension ref="A1:V135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9799,6 +9799,76 @@
       </c>
       <c r="V134" t="n">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-24 13:23:01</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C135" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D135" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G135" t="n">
+        <v>101.752</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I135" t="n">
+        <v>74.15674271934706</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2.071887600153405</v>
+      </c>
+      <c r="K135" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="L135" t="n">
+        <v>50</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N135" t="n">
+        <v>50</v>
+      </c>
+      <c r="O135" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R135" t="n">
+        <v>112.104</v>
+      </c>
+      <c r="S135" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T135" t="n">
+        <v>3997.79</v>
+      </c>
+      <c r="U135" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V135"/>
+  <dimension ref="A1:V136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9868,6 +9868,76 @@
         <v>-0.01</v>
       </c>
       <c r="V135" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-25 13:40:53</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D136" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G136" t="n">
+        <v>101.752</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I136" t="n">
+        <v>74.15674271934706</v>
+      </c>
+      <c r="J136" t="n">
+        <v>2.071887600153405</v>
+      </c>
+      <c r="K136" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="L136" t="n">
+        <v>50</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N136" t="n">
+        <v>50</v>
+      </c>
+      <c r="O136" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R136" t="n">
+        <v>112.104</v>
+      </c>
+      <c r="S136" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T136" t="n">
+        <v>3997.79</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V136" t="n">
         <v>0.13</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V136"/>
+  <dimension ref="A1:V137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9939,6 +9939,76 @@
       </c>
       <c r="V136" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:46:08</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C137" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D137" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G137" t="n">
+        <v>101.7001</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="I137" t="n">
+        <v>74.04911373707533</v>
+      </c>
+      <c r="J137" t="n">
+        <v>2.078474662354758</v>
+      </c>
+      <c r="K137" t="n">
+        <v>56.07</v>
+      </c>
+      <c r="L137" t="n">
+        <v>50</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="N137" t="n">
+        <v>50</v>
+      </c>
+      <c r="O137" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="P137" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R137" t="n">
+        <v>109.763</v>
+      </c>
+      <c r="S137" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T137" t="n">
+        <v>4010.5</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V137"/>
+  <dimension ref="A1:V138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10009,6 +10009,76 @@
       </c>
       <c r="V137" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:58:46</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D138" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G138" t="n">
+        <v>102.0877</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="I138" t="n">
+        <v>75.19951246952935</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2.078417653948609</v>
+      </c>
+      <c r="K138" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="L138" t="n">
+        <v>50</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-0.036</v>
+      </c>
+      <c r="N138" t="n">
+        <v>50</v>
+      </c>
+      <c r="O138" t="n">
+        <v>18.31</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R138" t="n">
+        <v>109.872</v>
+      </c>
+      <c r="S138" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T138" t="n">
+        <v>4010.39</v>
+      </c>
+      <c r="U138" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V138"/>
+  <dimension ref="A1:V139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10079,6 +10079,76 @@
       </c>
       <c r="V138" t="n">
         <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:37:21</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D139" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E139" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G139" t="n">
+        <v>102.4547</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I139" t="n">
+        <v>74.89481509013194</v>
+      </c>
+      <c r="J139" t="n">
+        <v>2.088627341231589</v>
+      </c>
+      <c r="K139" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="L139" t="n">
+        <v>50</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="N139" t="n">
+        <v>50</v>
+      </c>
+      <c r="O139" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R139" t="n">
+        <v>111.257</v>
+      </c>
+      <c r="S139" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T139" t="n">
+        <v>4030.09</v>
+      </c>
+      <c r="U139" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V139"/>
+  <dimension ref="A1:V140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10148,6 +10148,76 @@
         <v>-0.01</v>
       </c>
       <c r="V139" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:44:53</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D140" t="n">
+        <v>121.1877334510947</v>
+      </c>
+      <c r="E140" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G140" t="n">
+        <v>102.2209</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="I140" t="n">
+        <v>76.36680560818492</v>
+      </c>
+      <c r="J140" t="n">
+        <v>2.088912383262332</v>
+      </c>
+      <c r="K140" t="n">
+        <v>45.42</v>
+      </c>
+      <c r="L140" t="n">
+        <v>50</v>
+      </c>
+      <c r="M140" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="N140" t="n">
+        <v>50</v>
+      </c>
+      <c r="O140" t="n">
+        <v>17.79</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R140" t="n">
+        <v>110.514</v>
+      </c>
+      <c r="S140" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T140" t="n">
+        <v>4030.64</v>
+      </c>
+      <c r="U140" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V140" t="n">
         <v>0.08</v>
       </c>
     </row>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V140"/>
+  <dimension ref="A1:V141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10219,6 +10219,76 @@
       </c>
       <c r="V140" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:48:12</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C141" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D141" t="n">
+        <v>119.5466675649793</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G141" t="n">
+        <v>101.8616</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="I141" t="n">
+        <v>78.37163092661814</v>
+      </c>
+      <c r="J141" t="n">
+        <v>2.064549063507365</v>
+      </c>
+      <c r="K141" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L141" t="n">
+        <v>50</v>
+      </c>
+      <c r="M141" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="N141" t="n">
+        <v>50</v>
+      </c>
+      <c r="O141" t="n">
+        <v>17.41</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R141" t="n">
+        <v>111.931</v>
+      </c>
+      <c r="S141" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T141" t="n">
+        <v>3983.63</v>
+      </c>
+      <c r="U141" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V141" t="n">
+        <v>-0.02</v>
       </c>
     </row>
   </sheetData>

--- a/GMVM_v6.1_work.xlsx
+++ b/GMVM_v6.1_work.xlsx
@@ -616,7 +616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V141"/>
+  <dimension ref="A1:V142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10289,6 +10289,76 @@
       </c>
       <c r="V141" t="n">
         <v>-0.02</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-31 14:37:09</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>870.5</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="D142" t="n">
+        <v>119.5466675649793</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G142" t="n">
+        <v>101.9669</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="I142" t="n">
+        <v>78.97107353839885</v>
+      </c>
+      <c r="J142" t="n">
+        <v>2.009126527566156</v>
+      </c>
+      <c r="K142" t="n">
+        <v>49.65</v>
+      </c>
+      <c r="L142" t="n">
+        <v>50</v>
+      </c>
+      <c r="M142" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="N142" t="n">
+        <v>50</v>
+      </c>
+      <c r="O142" t="n">
+        <v>19.21</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>146.21</v>
+      </c>
+      <c r="R142" t="n">
+        <v>113.498</v>
+      </c>
+      <c r="S142" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T142" t="n">
+        <v>3876.69</v>
+      </c>
+      <c r="U142" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
